--- a/p6_deployment/data/spain/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA3"/>
+  <dimension ref="A1:BE9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,235 +460,255 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>h2h_35</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>is_rival_match</t>
         </is>
@@ -697,306 +717,1410 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDmOFmNG</t>
+          <t>M3h3GWnS</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45438.66666666666</v>
+        <v>45522.6875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>AD5WKzF</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>bs5KnIi</t>
-        </is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>148</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1481</v>
       </c>
       <c r="I2" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1481</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>20232024</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+        <v>20242025</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-16</v>
+      </c>
       <c r="Q2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4.333333333333334</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-6.333333333333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-1.666666666666664</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.666666666666664</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1266666666666667</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.6199999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="n">
-        <v>-6.999999999999998</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6.199999999999999</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-4.199999999999999</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-16.8</v>
-      </c>
-      <c r="W2" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.800000000000001</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-0.4999999999999998</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.5359999999999998</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>-4.333333333333334</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>76</v>
+      </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>-69289351.85185185</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2.824537037037036</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.5606481481481751</v>
+      </c>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>1.77939743205641</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-11.10967106327469</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-2.01712962962963</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-9.562962962962942</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-1.736994513631198</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-11.42916666666667</v>
+      </c>
       <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="n">
+      <c r="AX2" t="n">
+        <v>-0.1395720140695857</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-57038606.55263423</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-9.671305880745237</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bDmOFmNG</t>
+          <t>Eax2EqHs</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45438.66666666666</v>
+        <v>45522.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i   esp </t>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan  sevilla </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>148</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-5.166666666666666</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="V3" t="n">
+        <v>12.66666666666666</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-12.66666666666666</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.2941666666666667</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-0.4091666666666668</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>82</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="n">
+        <v>16755602.45310245</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-3.435425685425685</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.944083694083673</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>-4.439231041560237</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.763863031378563</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.3104617604617605</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.299855699855698</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.1811624228083855</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5.205050505050494</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="n">
+        <v>1.055534941249221</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9531051.225430883</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.048545346992555</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45521.6875</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>148</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>-25</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-11</v>
+      </c>
+      <c r="W4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.4024999999999999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="n">
+        <v>78.49166666666666</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>-34053333.33333333</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-2.416666666666664</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.452777777777783</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>0.4866629715313913</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-8.343237713438953</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-1.680555555555556</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-6.780555555555551</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-1.218155858834762</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-5.569444444444443</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="n">
+        <v>-0.3151747878638105</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-31762979.46371531</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-7.023123648919764</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alvendiz l 
+  esp </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>148</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Qkg2vOrk</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.4166666666666661</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4.583333333333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-6.833333333333336</v>
+      </c>
+      <c r="W5" t="n">
+        <v>6.833333333333336</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.416666666666667</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.04416666666666658</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.3433333333333333</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.5833333333333334</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1.333333333333334</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>69.24259259259259</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>-1.097880587641754</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3.61474288279905</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>0.05741341991342019</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="n">
+        <v>2.420057656236366</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5198553.288739739</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.401035382254989</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>h8oAv4Ts</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>AD5WKzFn</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G6" t="n">
+        <v>148</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>bs5KnIiT</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="O6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-9.666666666666666</v>
+      </c>
+      <c r="V6" t="n">
+        <v>14.66666666666666</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-14.66666666666666</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.09666666666666712</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.4666666666666668</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>74.9875</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>77.6875</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>-6378935.185185185</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.9054232804232782</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-6.158730158730123</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>2.386599706067955</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-6.183892790878005</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0.6216931216931214</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-2.186507936507951</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.4794486021833479</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-1.750992063492063</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>-4.945574857473332</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-7660067.448031845</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-2.785662844437198</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>148</v>
       </c>
-      <c r="J3" t="n">
+      <c r="H7" t="n">
         <v>1481</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>20232024</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-29</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-29</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.4166666666666661</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11.41666666666666</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-11.41666666666666</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-2.833333333333333</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.055833333333333</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-1.083333333333333</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.166666666666666</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>74.39583333333334</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>80.175</v>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>4340156.25</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>3.054166666666664</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.470138888888926</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>2.188409856696303</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.22108191102528</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.4166666666666665</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.700694444444451</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.2562558356676004</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.910416666666663</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="n">
+        <v>-1.517016371766118</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3469722.468697623</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>3.771099454274463</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45519.6875</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>148</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>A7v4ruhp</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.3333333333333357</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.8033333333333335</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>4.333333333333334</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>76.19166666666666</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>72.8125</v>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="n">
+        <v>-15380277.77777778</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2.279761904761909</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.8746031746031804</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>3.604409456090128</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-1.403460358502386</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.3849206349206349</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-3.533333333333346</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.8454735740450023</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-3.974999999999994</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>5.487914140014965</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-5236460.276418259</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.064265706282512</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45519.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>148</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>p2dFnNso</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6.333333333333332</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>12</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-12</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AA9" t="n">
         <v>-4</v>
       </c>
-      <c r="P3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-6.999999999999998</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6.199999999999999</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-4.199999999999999</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-16.8</v>
-      </c>
-      <c r="W3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.800000000000001</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-0.4999999999999998</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.5359999999999998</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>141</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-17057142.85714286</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>141</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-110300000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>-6.958333333333329</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-0.7678571428571428</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-1.597222222222221</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-4.285714285714292</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-1.305555555555556</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-36526388.88888889</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>3.375</v>
-      </c>
-      <c r="BA3" t="n">
+      <c r="AB9" t="n">
+        <v>0.4966666666666668</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.7066666666666667</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-5.666666666666666</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>74.28472222222223</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>73.13333333333334</v>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="n">
+        <v>10699442.34006734</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.1080808080808069</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-1.401388888888874</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>2.111665680765057</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.971705856255554</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.3412457912457914</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.197222222222209</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.3464606132307995</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.061868686868678</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="n">
+        <v>-2.093692694469098</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>6873241.860149856</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.541421423641893</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="n">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/spain/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE9"/>
+  <dimension ref="A1:BE13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,24 +500,24 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>h2h_35</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_35</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_3</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>result</t>
@@ -525,64 +525,64 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,45 +717,40 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>ng6idLW1</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.6875</v>
+        <v>45665.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">villanueva j  i 
   esp </t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>148</v>
       </c>
       <c r="H2" t="n">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>20242025</v>
+        <v>2025</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -764,127 +759,93 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>super cup</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>bs5KnIiT</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-16</v>
+        <v>-42</v>
       </c>
       <c r="P2" t="n">
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="R2" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="n">
-        <v>4.333333333333334</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-6.333333333333333</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-1.666666666666664</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.666666666666664</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.6666666666666661</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.1266666666666667</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.6199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-4.333333333333334</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>76</v>
-      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>-69289351.85185185</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.824537037037036</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>0.5606481481481751</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>-25300474.47493317</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3.497689926639815</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>1.77939743205641</v>
+        <v>-1.12898428731762</v>
       </c>
       <c r="AR2" t="n">
-        <v>-11.10967106327469</v>
+        <v>1.582131316797614</v>
       </c>
       <c r="AS2" t="n">
-        <v>-2.01712962962963</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-9.562962962962942</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-1.736994513631198</v>
-      </c>
+        <v>-1.769444444444446</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>-11.42916666666667</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>0.5532547699214341</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-20265495.23007856</v>
+      </c>
       <c r="AX2" t="n">
-        <v>-0.1395720140695857</v>
+        <v>1.234567901234556</v>
       </c>
       <c r="AY2" t="n">
-        <v>-57038606.55263423</v>
+        <v>-0.8079179948971473</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-9.671305880745237</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
+        <v>-2.958343311025942</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-3.519248035914714</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-5.65274590910839</v>
+      </c>
       <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
@@ -894,45 +855,40 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>CWcwKOO8</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45522.58333333334</v>
+        <v>45665.66666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>148</v>
       </c>
       <c r="H3" t="n">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>20242025</v>
+        <v>2025</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -941,129 +897,93 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>super cup</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>p2dFnNso</t>
         </is>
       </c>
       <c r="O3" t="n">
+        <v>16</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>12</v>
+      </c>
+      <c r="R3" t="n">
         <v>2</v>
       </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3</v>
-      </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="n">
-        <v>-5.166666666666666</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-6.75</v>
-      </c>
-      <c r="V3" t="n">
-        <v>12.66666666666666</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-12.66666666666666</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-0.2941666666666667</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-0.4091666666666668</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>78.25</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>82</v>
-      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="n">
-        <v>16755602.45310245</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-3.435425685425685</v>
-      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>1.944083694083673</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>56572175.7769824</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-1.801273760286296</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>-4.439231041560237</v>
+        <v>1.690462962962963</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.763863031378563</v>
+        <v>-0.4264984813482613</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.3104617604617605</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.299855699855698</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.1811624228083855</v>
-      </c>
+        <v>8.989629629629604</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>5.205050505050494</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>-2.732870370370371</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>62108518.51851852</v>
+      </c>
       <c r="AX3" t="n">
-        <v>1.055534941249221</v>
+        <v>-0.7056481481481853</v>
       </c>
       <c r="AY3" t="n">
-        <v>9531051.225430883</v>
+        <v>1.776534010336227</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.048545346992555</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
+        <v>9.481822436751884</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>10.7475</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>11.10241162443961</v>
+      </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
@@ -1073,32 +993,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>E1Xs9lu2</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45521.6875</v>
+        <v>45523.6875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1125,25 +1045,25 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>-25</v>
+        <v>-1</v>
       </c>
       <c r="P4" t="n">
-        <v>-25</v>
+        <v>-1</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1152,95 +1072,97 @@
         <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5</v>
+        <v>-1.333333333333334</v>
       </c>
       <c r="V4" t="n">
-        <v>-11</v>
+        <v>4.333333333333329</v>
       </c>
       <c r="W4" t="n">
-        <v>11</v>
+        <v>-4.333333333333329</v>
       </c>
       <c r="X4" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>11.66666666666667</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.666666666666668</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9800000000000002</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.7466666666666666</v>
+      </c>
+      <c r="AF4" t="n">
         <v>-0.6666666666666665</v>
       </c>
-      <c r="Y4" t="n">
-        <v>-0.6666666666666665</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-0.4024999999999999</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-1.25</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.75</v>
+        <v>4.333333333333334</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+        <v>-4.666666666666666</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>74.77777777777777</v>
+      </c>
       <c r="AK4" t="n">
-        <v>78.49166666666666</v>
+        <v>77.33703703703704</v>
       </c>
       <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>-34053333.33333333</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-2.416666666666664</v>
-      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>1.452777777777783</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>-12593893.4368101</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.37686326019659</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>0.4866629715313913</v>
+        <v>-0.6797839506172838</v>
       </c>
       <c r="AR4" t="n">
-        <v>-8.343237713438953</v>
+        <v>3.491117524450857</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1.680555555555556</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>-6.780555555555551</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-1.218155858834762</v>
-      </c>
+        <v>-5.499614197530875</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>-5.569444444444443</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
+        <v>-0.8170524691358025</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-23986265.43209876</v>
+      </c>
       <c r="AX4" t="n">
-        <v>-0.3151747878638105</v>
+        <v>6.601620370370341</v>
       </c>
       <c r="AY4" t="n">
-        <v>-31762979.46371531</v>
+        <v>-0.03904552237885572</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-7.023123648919764</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
+        <v>-1.884786663953335</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-4.389891975308615</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-3.092088312921661</v>
+      </c>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
@@ -1250,32 +1172,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45523.58333333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">alvendiz l 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1302,106 +1224,108 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>IilCZTta</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Qkg2vOrk</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4166666666666661</v>
+        <v>-1.4</v>
       </c>
       <c r="U5" t="n">
-        <v>4.583333333333334</v>
+        <v>-1.066666666666667</v>
       </c>
       <c r="V5" t="n">
-        <v>-6.833333333333336</v>
+        <v>2.933333333333337</v>
       </c>
       <c r="W5" t="n">
-        <v>6.833333333333336</v>
+        <v>-2.933333333333337</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.06666666666666665</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.416666666666667</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.04416666666666658</v>
+        <v>4.866666666666665</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.3433333333333333</v>
+        <v>-2.933333333333333</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.3333333333333334</v>
+        <v>0.1066666666666665</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.3341666666666666</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.5833333333333334</v>
+        <v>1.133333333333334</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.4166666666666667</v>
+        <v>-0.8666666666666667</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1.333333333333334</v>
+        <v>-1.266666666666669</v>
       </c>
       <c r="AI5" t="n">
-        <v>-4.25</v>
+        <v>0.8666666666666654</v>
       </c>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="n">
-        <v>69.24259259259259</v>
-      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="n">
-        <v>-1.097880587641754</v>
-      </c>
+      <c r="AO5" t="n">
+        <v>388681.1091958154</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-2.522980804598447</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>3.61474288279905</v>
+        <v>0.1540372753607926</v>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="n">
-        <v>0.05741341991342019</v>
-      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="n">
-        <v>2.420057656236366</v>
-      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>5198553.288739739</v>
+        <v>-0.06167582417582418</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.401035382254989</v>
+        <v>-1.314926576691292</v>
       </c>
       <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
+      <c r="BB5" t="n">
+        <v>1.35256812903873</v>
+      </c>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
@@ -1411,32 +1335,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>M3h3GWnS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45520.6875</v>
+        <v>45522.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1463,124 +1387,122 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-4</v>
+        <v>-16</v>
       </c>
       <c r="P6" t="n">
         <v>-4</v>
       </c>
       <c r="Q6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-1.666666666666664</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.666666666666664</v>
+      </c>
+      <c r="X6" t="n">
         <v>-2</v>
       </c>
-      <c r="R6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-9.666666666666666</v>
-      </c>
-      <c r="V6" t="n">
-        <v>14.66666666666666</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-14.66666666666666</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.6666666666666665</v>
-      </c>
       <c r="Y6" t="n">
-        <v>0.6666666666666665</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>-0.6666666666666661</v>
       </c>
       <c r="AA6" t="n">
-        <v>-2.333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.09666666666666712</v>
+        <v>4.333333333333334</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.4666666666666668</v>
+        <v>-6.333333333333333</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>0.1266666666666667</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.6199999999999999</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.3333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.6666666666666667</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.6666666666666661</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.3333333333333339</v>
+        <v>-4.333333333333334</v>
       </c>
       <c r="AJ6" t="n">
-        <v>74.9875</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>77.6875</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="n">
-        <v>-6378935.185185185</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-0.9054232804232782</v>
-      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>-6.158730158730123</v>
-      </c>
-      <c r="AP6" t="inlineStr"/>
+        <v>-56572175.7769824</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.801273760286296</v>
+      </c>
       <c r="AQ6" t="n">
-        <v>2.386599706067955</v>
+        <v>-1.690462962962963</v>
       </c>
       <c r="AR6" t="n">
-        <v>-6.183892790878005</v>
+        <v>0.4264984813482613</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.6216931216931214</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>-2.186507936507951</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-0.4794486021833479</v>
-      </c>
+        <v>-8.989629629629604</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
-        <v>-1.750992063492063</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
+        <v>2.732870370370371</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-62108518.51851852</v>
+      </c>
       <c r="AX6" t="n">
-        <v>-4.945574857473332</v>
+        <v>0.7056481481481853</v>
       </c>
       <c r="AY6" t="n">
-        <v>-7660067.448031845</v>
+        <v>-1.776534010336227</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-2.785662844437198</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
+        <v>-9.481822436751884</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-10.7475</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-11.10241162443961</v>
+      </c>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="n">
@@ -1590,32 +1512,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>Eax2EqHs</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45520.58333333334</v>
+        <v>45522.58333333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1642,124 +1564,124 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="O7" t="n">
         <v>2</v>
       </c>
       <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4166666666666661</v>
+        <v>1.25</v>
       </c>
       <c r="U7" t="n">
-        <v>-5.25</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="V7" t="n">
-        <v>11.41666666666666</v>
+        <v>12.66666666666666</v>
       </c>
       <c r="W7" t="n">
-        <v>-11.41666666666666</v>
+        <v>-12.66666666666666</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>-2.833333333333333</v>
+        <v>-3.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.055833333333333</v>
+        <v>-5.166666666666666</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.4999999999999997</v>
+        <v>-6.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.083333333333333</v>
+        <v>-0.2941666666666667</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.5</v>
+        <v>-0.4091666666666668</v>
       </c>
       <c r="AF7" t="n">
         <v>1.166666666666667</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1.083333333333333</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.166666666666666</v>
+        <v>-0.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>74.39583333333334</v>
+        <v>78.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>80.175</v>
+        <v>82</v>
       </c>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="n">
-        <v>4340156.25</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>3.054166666666664</v>
-      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>1.470138888888926</v>
-      </c>
-      <c r="AP7" t="inlineStr"/>
+        <v>9681538.40814982</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-4.539468703599145</v>
+      </c>
       <c r="AQ7" t="n">
-        <v>2.188409856696303</v>
+        <v>0.2999929854096521</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.22108191102528</v>
+        <v>1.01762134805611</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.4166666666666665</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.700694444444451</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.2562558356676004</v>
-      </c>
+        <v>3.508768237934916</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="n">
-        <v>1.910416666666663</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
+        <v>-3.436651234567904</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>17315192.55050505</v>
+      </c>
       <c r="AX7" t="n">
-        <v>-1.517016371766118</v>
+        <v>1.869367283950623</v>
       </c>
       <c r="AY7" t="n">
-        <v>3469722.468697623</v>
+        <v>0.2097359725620596</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.771099454274463</v>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
+        <v>0.9208483645983705</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.469753086419743</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.709641811489632</v>
+      </c>
       <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="n">
@@ -1769,32 +1691,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>KbKTWiX8</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45519.6875</v>
+        <v>45521.6875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
+          <t xml:space="preserve">villanueva j  i 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1821,124 +1743,122 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>A7v4ruhp</t>
+          <t>bs5KnIiT</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>-25</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>-5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="U8" t="n">
-        <v>-5</v>
+        <v>-0.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3333333333333357</v>
+        <v>-11</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3333333333333357</v>
+        <v>11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.666666666666667</v>
+        <v>-2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.8033333333333335</v>
+        <v>-1</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.6666666666666667</v>
+        <v>-0.4024999999999999</v>
       </c>
       <c r="AF8" t="n">
-        <v>-1</v>
+        <v>-1.25</v>
       </c>
       <c r="AG8" t="n">
         <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.333333333333334</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>76.19166666666666</v>
-      </c>
+        <v>3.25</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="n">
-        <v>72.8125</v>
+        <v>78.49166666666666</v>
       </c>
       <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="n">
-        <v>-15380277.77777778</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>2.279761904761909</v>
-      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>0.8746031746031804</v>
-      </c>
-      <c r="AP8" t="inlineStr"/>
+        <v>-32134563.93788243</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.499958732214921</v>
+      </c>
       <c r="AQ8" t="n">
-        <v>3.604409456090128</v>
+        <v>-1.601851851851852</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.403460358502386</v>
+        <v>-0.3881106570444217</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.3849206349206349</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>-3.533333333333346</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0.8454735740450023</v>
-      </c>
+        <v>-5.680555555555557</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="n">
-        <v>-3.974999999999994</v>
-      </c>
-      <c r="AW8" t="inlineStr"/>
+        <v>-2.011574074074076</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-30068749.99999999</v>
+      </c>
       <c r="AX8" t="n">
-        <v>5.487914140014965</v>
+        <v>0.9953703703703525</v>
       </c>
       <c r="AY8" t="n">
-        <v>-5236460.276418259</v>
+        <v>-1.225195504171897</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.064265706282512</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
+        <v>-6.538574981734797</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-5.506944444444457</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-7.857951388495124</v>
+      </c>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="n">
@@ -1948,32 +1868,32 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>ruUIA1G6</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45519.58333333334</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">alvendiz l 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2000,127 +1920,825 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>p2dFnNso</t>
+          <t>Qkg2vOrk</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>6.333333333333332</v>
+        <v>0.5</v>
       </c>
       <c r="U9" t="n">
-        <v>-5.333333333333334</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="V9" t="n">
-        <v>12</v>
+        <v>-6.833333333333336</v>
       </c>
       <c r="W9" t="n">
-        <v>-12</v>
+        <v>6.833333333333336</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>-4</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.4966666666666668</v>
+        <v>-0.4166666666666661</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.7066666666666667</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.6666666666666667</v>
+        <v>-0.04416666666666658</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>0.3433333333333333</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.6666666666666667</v>
+        <v>-0.5833333333333334</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.333333333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AH9" t="n">
-        <v>-14</v>
+        <v>-1.333333333333334</v>
       </c>
       <c r="AI9" t="n">
-        <v>-5.666666666666666</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>74.28472222222223</v>
-      </c>
+        <v>-4.25</v>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="n">
-        <v>73.13333333333334</v>
+        <v>69.24259259259259</v>
       </c>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="n">
-        <v>10699442.34006734</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-0.1080808080808069</v>
-      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>-1.401388888888874</v>
-      </c>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="n">
-        <v>2.111665680765057</v>
-      </c>
+        <v>5269724.278337177</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.6828342922318633</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="n">
-        <v>2.971705856255554</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.3412457912457914</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.197222222222209</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.3464606132307995</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.061868686868678</v>
-      </c>
+        <v>2.89386719422842</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="n">
-        <v>-2.093692694469098</v>
-      </c>
+      <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="n">
-        <v>6873241.860149856</v>
+        <v>0.05023674242424248</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.541421423641893</v>
+        <v>3.732628239028202</v>
       </c>
       <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
+      <c r="BB9" t="n">
+        <v>3.641528715641854</v>
+      </c>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>148</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>14.66666666666666</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-14.66666666666666</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-9.666666666666666</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.09666666666666712</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.4666666666666668</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>74.9875</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>77.6875</v>
+      </c>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>-7539604.471573318</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.442062621597341</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.5992063492063489</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-5.21487800028919</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-2.20634920634923</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>-0.9880952380952372</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-6223015.873015871</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-6.170634920634882</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.4634569208498232</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-2.749197413124989</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-1.724206349206355</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-6.194618313230379</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>148</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="V11" t="n">
+        <v>11.41666666666666</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-11.41666666666666</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-2.833333333333333</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.4166666666666661</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.055833333333333</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-1.083333333333333</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.166666666666666</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>74.39583333333334</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>80.175</v>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>3527458.471798753</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.22569367436779</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.4513888888888886</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-1.424525129782381</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.287037037037038</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>3.097222222222221</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>3930208.333333333</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.8865740740741046</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.2389297385620914</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.805204191389251</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.493055555555557</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.176925183477081</v>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45519.6875</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>148</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>A7v4ruhp</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.3333333333333357</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.8033333333333335</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4.333333333333334</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>76.19166666666666</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>72.8125</v>
+      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="n">
+        <v>-4429940.02256773</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3.648595116184126</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.3972222222222221</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.893591539179766</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-3.333333333333343</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>2.358333333333334</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-15000138.88888889</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.9902777777777771</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.8867192018507803</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.247021966681402</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-3.954166666666666</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-1.360045357549239</v>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45519.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>148</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>p2dFnNso</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="V13" t="n">
+        <v>12</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>6.333333333333332</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.4966666666666668</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.7066666666666667</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-5.666666666666666</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>74.28472222222223</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>73.13333333333334</v>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="n">
+        <v>8214433.561541989</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.311091928190034</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.2585818502485171</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-2.708662121789956</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.946825396825403</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="n">
+        <v>-0.2833854417187744</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>10188076.19849287</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.8143738977072132</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.3781367140677783</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.374122818368392</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.050196408529743</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>3.491962026896942</v>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="n">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/spain/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_constructed.xlsx
@@ -525,187 +525,187 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -806,48 +806,48 @@
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>3.380078668220012</v>
+      </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>-25300474.47493317</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>3.497689926639815</v>
-      </c>
+        <v>-19813699.49494949</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>-1.12898428731762</v>
+        <v>-3.441792929292944</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.582131316797614</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-1.769444444444446</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+        <v>-5.794217169788269</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>1.777040772401193</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-25836411.93028653</v>
+      </c>
       <c r="AV2" t="n">
-        <v>0.5532547699214341</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-20265495.23007856</v>
-      </c>
+        <v>1.078703703703724</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>1.234567901234556</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-0.8079179948971473</v>
-      </c>
+        <v>0.5448653198653162</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>-2.958343311025942</v>
+        <v>-1.676388888888894</v>
       </c>
       <c r="BA2" t="n">
-        <v>-3.519248035914714</v>
+        <v>-3.252028187468255</v>
       </c>
       <c r="BB2" t="n">
-        <v>-5.65274590910839</v>
+        <v>-1.095917508417508</v>
       </c>
       <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
+      <c r="BD2" t="n">
+        <v>-0.8200419137926147</v>
+      </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -944,48 +944,48 @@
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
+      <c r="AM3" t="n">
+        <v>-1.908196887349387</v>
+      </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>56572175.7769824</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-1.801273760286296</v>
-      </c>
+        <v>64559143.51851852</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>1.690462962962963</v>
+        <v>10.99375000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.4264984813482613</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>8.989629629629604</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
+        <v>11.12648929231888</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>-0.2313083945172991</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>57740083.69611983</v>
+      </c>
       <c r="AV3" t="n">
-        <v>-2.732870370370371</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>62108518.51851852</v>
-      </c>
+        <v>-0.5668981481481694</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>-0.7056481481481853</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.776534010336227</v>
-      </c>
+        <v>-2.72662037037037</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>9.481822436751884</v>
+        <v>9.204629629629608</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.7475</v>
+        <v>9.513038854755578</v>
       </c>
       <c r="BB3" t="n">
-        <v>11.10241162443961</v>
+        <v>1.800462962962963</v>
       </c>
       <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
+      <c r="BD3" t="n">
+        <v>1.773749733388831</v>
+      </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -1068,103 +1068,67 @@
       <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-1.333333333333334</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4.333333333333329</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-4.333333333333329</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>11.66666666666667</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.666666666666668</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.9800000000000002</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.7466666666666666</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-0.6666666666666665</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>4.333333333333334</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-4.666666666666666</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>74.77777777777777</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>77.33703703703704</v>
-      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>2.734735056610056</v>
+      </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>-12593893.4368101</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.37686326019659</v>
-      </c>
+        <v>-24523726.85185185</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>-0.6797839506172838</v>
+        <v>-4.728009259259252</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.491117524450857</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-5.499614197530875</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
+        <v>-2.958634074259081</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>3.682715548340553</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-12573512.06085581</v>
+      </c>
       <c r="AV4" t="n">
-        <v>-0.8170524691358025</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>-23986265.43209876</v>
-      </c>
+        <v>6.174768518518505</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>6.601620370370341</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-0.03904552237885572</v>
-      </c>
+        <v>-1.351851851851855</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>-1.884786663953335</v>
+        <v>-5.923611111111128</v>
       </c>
       <c r="BA4" t="n">
-        <v>-4.389891975308615</v>
+        <v>-1.679412774725279</v>
       </c>
       <c r="BB4" t="n">
-        <v>-3.092088312921661</v>
+        <v>-0.7228009259259258</v>
       </c>
       <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
+      <c r="BD4" t="n">
+        <v>0.03853906510156513</v>
+      </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
@@ -1247,87 +1211,55 @@
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-1.066666666666667</v>
-      </c>
-      <c r="V5" t="n">
-        <v>2.933333333333337</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-2.933333333333337</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.06666666666666665</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.7333333333333334</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>4.866666666666665</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-2.933333333333333</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.1066666666666665</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.3341666666666666</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.133333333333334</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-0.8666666666666667</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-1.266666666666669</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.8666666666666654</v>
-      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>-2.522980804598447</v>
+      </c>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
-        <v>388681.1091958154</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-2.522980804598447</v>
-      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
+        <v>1.35256812903873</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
         <v>0.1540372753607926</v>
       </c>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>388681.1091958154</v>
+      </c>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="n">
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>-1.314926576691292</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="n">
         <v>-0.06167582417582418</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>-1.314926576691292</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="n">
-        <v>1.35256812903873</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
@@ -1410,101 +1342,67 @@
       <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.333333333333333</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-1.666666666666664</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.666666666666664</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-0.6666666666666661</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>4.333333333333334</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-6.333333333333333</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.1266666666666667</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-0.6199999999999999</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-4.333333333333334</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>76</v>
-      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>1.908196887349387</v>
+      </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>-56572175.7769824</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.801273760286296</v>
-      </c>
+        <v>-64559143.51851852</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="n">
-        <v>-1.690462962962963</v>
+        <v>-10.99375000000001</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.4264984813482613</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-8.989629629629604</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
+        <v>-11.12648929231888</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0.2313083945172991</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-57740083.69611983</v>
+      </c>
       <c r="AV6" t="n">
-        <v>2.732870370370371</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-62108518.51851852</v>
-      </c>
+        <v>0.5668981481481694</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>0.7056481481481853</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-1.776534010336227</v>
-      </c>
+        <v>2.72662037037037</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="n">
-        <v>-9.481822436751884</v>
+        <v>-9.204629629629608</v>
       </c>
       <c r="BA6" t="n">
-        <v>-10.7475</v>
+        <v>-9.513038854755578</v>
       </c>
       <c r="BB6" t="n">
-        <v>-11.10241162443961</v>
+        <v>-1.800462962962963</v>
       </c>
       <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>-1.773749733388831</v>
+      </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
@@ -1587,103 +1485,67 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="V7" t="n">
-        <v>12.66666666666666</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-12.66666666666666</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-5.166666666666666</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-6.75</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.2941666666666667</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-0.4091666666666668</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>78.25</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>82</v>
-      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
+      <c r="AM7" t="n">
+        <v>-4.533136685174732</v>
+      </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>9681538.40814982</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-4.539468703599145</v>
-      </c>
+        <v>16803450.12626263</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="n">
-        <v>0.2999929854096521</v>
+        <v>5.27916666666664</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01762134805611</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3.508768237934916</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
+        <v>4.7975468191229</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0.9432359307359093</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9892809.703204405</v>
+      </c>
       <c r="AV7" t="n">
-        <v>-3.436651234567904</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>17315192.55050505</v>
-      </c>
+        <v>2.052083333333314</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>1.869367283950623</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0.2097359725620596</v>
-      </c>
+        <v>-3.378472222222225</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="n">
-        <v>0.9208483645983705</v>
+        <v>3.389898989898995</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.469753086419743</v>
+        <v>1.025512892904203</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.709641811489632</v>
+        <v>0.2981691919191918</v>
       </c>
       <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
+      <c r="BD7" t="n">
+        <v>0.1972075961478135</v>
+      </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
@@ -1766,101 +1628,67 @@
       <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-11</v>
-      </c>
-      <c r="W8" t="n">
-        <v>11</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-0.4024999999999999</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>3.25</v>
-      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="n">
-        <v>78.49166666666666</v>
-      </c>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
+      <c r="AM8" t="n">
+        <v>0.499958732214921</v>
+      </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
+        <v>-30068749.99999999</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>-5.506944444444457</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-7.857951388495124</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>-0.3881106570444217</v>
+      </c>
+      <c r="AU8" t="n">
         <v>-32134563.93788243</v>
       </c>
-      <c r="AP8" t="n">
-        <v>0.499958732214921</v>
-      </c>
-      <c r="AQ8" t="n">
+      <c r="AV8" t="n">
+        <v>0.9953703703703525</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>-2.011574074074076</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="n">
+        <v>-5.680555555555557</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-6.538574981734797</v>
+      </c>
+      <c r="BB8" t="n">
         <v>-1.601851851851852</v>
       </c>
-      <c r="AR8" t="n">
-        <v>-0.3881106570444217</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>-5.680555555555557</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="n">
-        <v>-2.011574074074076</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>-30068749.99999999</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0.9953703703703525</v>
-      </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="n">
         <v>-1.225195504171897</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>-6.538574981734797</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>-5.506944444444457</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>-7.857951388495124</v>
-      </c>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
@@ -1939,89 +1767,55 @@
       <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-6.833333333333336</v>
-      </c>
-      <c r="W9" t="n">
-        <v>6.833333333333336</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.3333333333333334</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.416666666666667</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-0.4166666666666661</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.583333333333334</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-0.04416666666666658</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.3433333333333333</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-0.5833333333333334</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-1.333333333333334</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-4.25</v>
-      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="n">
-        <v>69.24259259259259</v>
-      </c>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
+      <c r="AM9" t="n">
+        <v>-0.6828342922318633</v>
+      </c>
       <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="n">
-        <v>5269724.278337177</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>-0.6828342922318633</v>
-      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="n">
+        <v>3.641528715641854</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
         <v>2.89386719422842</v>
       </c>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>5269724.278337177</v>
+      </c>
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="n">
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>3.732628239028202</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="n">
         <v>0.05023674242424248</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>3.732628239028202</v>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="n">
-        <v>3.641528715641854</v>
-      </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
@@ -2104,103 +1898,67 @@
       <c r="S10" t="n">
         <v>0</v>
       </c>
-      <c r="T10" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>14.66666666666666</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-14.66666666666666</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-9.666666666666666</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.09666666666666712</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-0.4666666666666668</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-0.6666666666666661</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>74.9875</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>77.6875</v>
-      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
+      <c r="AM10" t="n">
+        <v>2.442062621597341</v>
+      </c>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
+        <v>-6223015.873015871</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>-1.724206349206355</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-6.194618313230379</v>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>-5.21487800028919</v>
+      </c>
+      <c r="AU10" t="n">
         <v>-7539604.471573318</v>
       </c>
-      <c r="AP10" t="n">
-        <v>2.442062621597341</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="AV10" t="n">
+        <v>-6.170634920634882</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>-0.9880952380952372</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>-2.20634920634923</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-2.749197413124989</v>
+      </c>
+      <c r="BB10" t="n">
         <v>-0.5992063492063489</v>
       </c>
-      <c r="AR10" t="n">
-        <v>-5.21487800028919</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-2.20634920634923</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="n">
-        <v>-0.9880952380952372</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-6223015.873015871</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-6.170634920634882</v>
-      </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="n">
         <v>-0.4634569208498232</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>-2.749197413124989</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-1.724206349206355</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-6.194618313230379</v>
-      </c>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
@@ -2283,103 +2041,67 @@
       <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-0.666666666666667</v>
-      </c>
-      <c r="V11" t="n">
-        <v>11.41666666666666</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-11.41666666666666</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-2.833333333333333</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.4166666666666661</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-5.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.055833333333333</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-0.4999999999999997</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>-1.083333333333333</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.166666666666666</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>74.39583333333334</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>80.175</v>
-      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
+      <c r="AM11" t="n">
+        <v>2.200462339779541</v>
+      </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
-        <v>3527458.471798753</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>2.22569367436779</v>
-      </c>
+        <v>4132083.333333333</v>
+      </c>
+      <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="n">
+        <v>1.668055555555554</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.133462152023284</v>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>-1.476770130248894</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3450645.318005157</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.053240740740762</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>3.193055555555553</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>3.582870370370372</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>3.739340505462295</v>
+      </c>
+      <c r="BB11" t="n">
         <v>0.4513888888888886</v>
       </c>
-      <c r="AR11" t="n">
-        <v>-1.424525129782381</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>3.287037037037038</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="n">
-        <v>3.097222222222221</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>3930208.333333333</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0.8865740740741046</v>
-      </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="n">
         <v>0.2389297385620914</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>3.805204191389251</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.493055555555557</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.176925183477081</v>
-      </c>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
@@ -2462,103 +2184,67 @@
       <c r="S12" t="n">
         <v>0</v>
       </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.3333333333333357</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-0.3333333333333357</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.666666666666666</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-0.8033333333333335</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>4.333333333333334</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>76.19166666666666</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>72.8125</v>
-      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
+      <c r="AM12" t="n">
+        <v>3.648595116184126</v>
+      </c>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
+        <v>-15000138.88888889</v>
+      </c>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>-3.954166666666666</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-1.360045357549239</v>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>4.893591539179766</v>
+      </c>
+      <c r="AU12" t="n">
         <v>-4429940.02256773</v>
       </c>
-      <c r="AP12" t="n">
-        <v>3.648595116184126</v>
-      </c>
-      <c r="AQ12" t="n">
+      <c r="AV12" t="n">
+        <v>0.9902777777777771</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="n">
+        <v>2.358333333333334</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>-3.333333333333343</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.247021966681402</v>
+      </c>
+      <c r="BB12" t="n">
         <v>0.3972222222222221</v>
       </c>
-      <c r="AR12" t="n">
-        <v>4.893591539179766</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-3.333333333333343</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="n">
-        <v>2.358333333333334</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-15000138.88888889</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0.9902777777777771</v>
-      </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="n">
         <v>0.8867192018507803</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>1.247021966681402</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>-3.954166666666666</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-1.360045357549239</v>
-      </c>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
@@ -2641,103 +2327,67 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-0.333333333333333</v>
-      </c>
-      <c r="V13" t="n">
-        <v>12</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>6.333333333333332</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>-5.333333333333334</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.4966666666666668</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>-0.7066666666666667</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>-14</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>-5.666666666666666</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>74.28472222222223</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>73.13333333333334</v>
-      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
+      <c r="AM13" t="n">
+        <v>2.193480669770231</v>
+      </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="n">
-        <v>8214433.561541989</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.311091928190034</v>
-      </c>
+        <v>10639871.93362194</v>
+      </c>
+      <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="n">
-        <v>0.2585818502485171</v>
+        <v>3.127651515151513</v>
       </c>
       <c r="AR13" t="n">
-        <v>-2.708662121789956</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.946825396825403</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
+        <v>3.350490766217064</v>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>-2.513752666186377</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7678496.106188629</v>
+      </c>
       <c r="AV13" t="n">
-        <v>-0.2833854417187744</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>10188076.19849287</v>
-      </c>
+        <v>-0.9702380952380452</v>
+      </c>
+      <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="n">
-        <v>-0.8143738977072132</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0.3781367140677783</v>
-      </c>
+        <v>-0.2917748917748924</v>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="n">
-        <v>5.374122818368392</v>
+        <v>3.039880952380955</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.050196408529743</v>
+        <v>5.080437941926078</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.491962026896942</v>
+        <v>0.2916486291486293</v>
       </c>
       <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
+      <c r="BD13" t="n">
+        <v>0.3660127951723109</v>
+      </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>

--- a/p6_deployment/data/spain/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,267 +450,242 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>id_team_home</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>h2h_35</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
+          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+          <t>dif_mean_age_player_start</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>is_rival_match</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>is_rival_match</t>
         </is>
       </c>
     </row>
@@ -730,127 +705,120 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>IP5zl0cJ</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>SKbpVP5K</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>148</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1484</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>2025</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>super cup</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>0Q3vjDhH</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>bs5KnIiT</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>-42</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>-2</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>-12</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
+        <v>0.9673996913580254</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.5290895061728413</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-2.392785493827162</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-21467361.1111111</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.9643367566498202</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-3.464930555555554</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.263340021912427</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-1.188310185185185</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-5.481085751106946</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-27339071.97269149</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-4.041770926062227</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.651140094643594</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>3.380078668220012</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>-19813699.49494949</v>
-      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>-3.441792929292944</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-5.794217169788269</v>
-      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>1.777040772401193</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-25836411.93028653</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.078703703703724</v>
-      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>0.5448653198653162</v>
-      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>-1.676388888888894</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-3.252028187468255</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-1.095917508417508</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>-0.8200419137926147</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -868,127 +836,120 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>W8mj7MDD</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>4jDQxrbf</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>148</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1484</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>2025</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>super cup</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>p2dFnNso</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>16</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>12</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>2</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
+        <v>-1.308207070707027</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-2.240446127946129</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7.488173400673404</v>
+      </c>
+      <c r="W3" t="n">
+        <v>53211254.20875421</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.739018428574349</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>9.462878787878807</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.8960641423635138</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.542171717171717</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>10.77358227481584</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>57261198.95546704</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>8.721836734172271</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-2.129850321462168</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="n">
-        <v>-1.908196887349387</v>
-      </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="n">
-        <v>64559143.51851852</v>
-      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="n">
-        <v>10.99375000000001</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>11.12648929231888</v>
-      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="n">
-        <v>-0.2313083945172991</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>57740083.69611983</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-0.5668981481481694</v>
-      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="n">
-        <v>-2.72662037037037</v>
-      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="n">
-        <v>9.204629629629608</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>9.513038854755578</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.800462962962963</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="n">
-        <v>1.773749733388831</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AZ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1011,127 +972,122 @@
   villarreal </t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>lUatW5jE</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>jaarqpLQ</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>148</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>1481</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>20242025</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>KWIuYKwG</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>AZ18LjKN</t>
         </is>
-      </c>
-      <c r="O4" t="n">
-        <v>-1</v>
       </c>
       <c r="P4" t="n">
         <v>-1</v>
       </c>
       <c r="Q4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R4" t="n">
         <v>4</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>-1</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
+        <v>5.278356481481524</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-2.435763888888886</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-6.582754629629633</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-23228472.22222222</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.2603361958818617</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-4.822916666666657</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.408901312718086</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.8981481481481477</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-2.436867981841857</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-10675560.09931385</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-2.151501379060392</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9503994360902297</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>2.734735056610056</v>
-      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="n">
-        <v>-24523726.85185185</v>
-      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="n">
-        <v>-4.728009259259252</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-2.958634074259081</v>
-      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="n">
-        <v>3.682715548340553</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-12573512.06085581</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>6.174768518518505</v>
-      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="n">
-        <v>-1.351851851851855</v>
-      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="n">
-        <v>-5.923611111111128</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>-1.679412774725279</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-0.7228009259259258</v>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="n">
-        <v>0.03853906510156513</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1154,115 +1110,122 @@
   valladolid </t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>zkpajjvm</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>QFfPdh1J</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>148</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1481</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>20242025</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>IilCZTta</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>fmK213Ku</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>-7</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>-2</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>5</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
+        <v>-2.778935185185162</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-1.541666666666668</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-1.625000000000014</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-1036111.111111111</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1050673217905496</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.4166666666666572</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.6852096467857791</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.004629629629629539</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.6851613911757255</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-527661.9736612202</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-1.576698485861385</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-1.282833491015992</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
-        <v>-2.522980804598447</v>
-      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="n">
-        <v>1.35256812903873</v>
-      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="n">
-        <v>0.1540372753607926</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>388681.1091958154</v>
-      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="n">
-        <v>-1.314926576691292</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="n">
-        <v>-0.06167582417582418</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1285,127 +1248,122 @@
   palma de mallorca </t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>4jDQxrbf</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>W8mj7MDD</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>148</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>1481</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>20242025</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4AuIPRuq</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>U3wM1J72</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>-16</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-4</v>
       </c>
       <c r="Q6" t="n">
         <v>-4</v>
       </c>
       <c r="R6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S6" t="n">
         <v>-1</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
+        <v>1.308207070707027</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.240446127946129</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-7.488173400673404</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-53211254.20875421</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-1.739018428574349</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-9.462878787878807</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.8960641423635138</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-1.542171717171717</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-10.77358227481584</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-57261198.95546704</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-8.721836734172271</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.129850321462168</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="n">
-        <v>1.908196887349387</v>
-      </c>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
-        <v>-64559143.51851852</v>
-      </c>
+      <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="n">
-        <v>-10.99375000000001</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-11.12648929231888</v>
-      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="n">
-        <v>0.2313083945172991</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-57740083.69611983</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.5668981481481694</v>
-      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="n">
-        <v>2.72662037037037</v>
-      </c>
+      <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="n">
-        <v>-9.204629629629608</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-9.513038854755578</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-1.800462962962963</v>
-      </c>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="n">
-        <v>-1.773749733388831</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AZ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1428,127 +1386,122 @@
   san sebastian </t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>jNvak2f3</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>8bcjFy6O</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>148</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>1481</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>20242025</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>IJEltJ2H</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>EJmuzs93</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>2</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>7</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
+        <v>1.867708333333297</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-3.136458333333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3.729135101010101</v>
+      </c>
+      <c r="W7" t="n">
+        <v>17979561.23737374</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.2682422098147215</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.603124999999977</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.2910971227475443</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.3762941919191918</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.906691981105595</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11186211.25158292</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.9457345087851508</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-4.51046917978411</v>
+      </c>
+      <c r="AF7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="n">
-        <v>-4.533136685174732</v>
-      </c>
+      <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="n">
-        <v>16803450.12626263</v>
-      </c>
+      <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="n">
-        <v>5.27916666666664</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>4.7975468191229</v>
-      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="n">
-        <v>0.9432359307359093</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>9892809.703204405</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.052083333333314</v>
-      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="n">
-        <v>-3.378472222222225</v>
-      </c>
+      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="n">
-        <v>3.389898989898995</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.025512892904203</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0.2981691919191918</v>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="n">
-        <v>0.1972075961478135</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AZ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1571,127 +1524,122 @@
   valencia </t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>CQeaytrD</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>SKbpVP5K</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>148</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>1481</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>20242025</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>UDgEKBbq</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>bs5KnIiT</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>-25</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>-5</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>-9</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>-2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
+        <v>-0.6892361111111143</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-3.206597222222225</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-10.08159722222223</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-35668888.88888888</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-1.239402116126945</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-8.381944444444443</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.1664886421422693</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-1.595486111111111</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-8.735777858678304</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-35055056.96264707</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-8.178752744839727</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.3225403346970808</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="n">
-        <v>0.499958732214921</v>
-      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="n">
-        <v>-30068749.99999999</v>
-      </c>
+      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="n">
-        <v>-5.506944444444457</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-7.857951388495124</v>
-      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="n">
-        <v>-0.3881106570444217</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>-32134563.93788243</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.9953703703703525</v>
-      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="n">
-        <v>-2.011574074074076</v>
-      </c>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="n">
-        <v>-5.680555555555557</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>-6.538574981734797</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>-1.601851851851852</v>
-      </c>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="n">
-        <v>-1.225195504171897</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1714,111 +1662,106 @@
   pamplona </t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>ETdxjU8a</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Mi0rXQg7</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>148</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>1481</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>20242025</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>KWIuYKwG</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Qkg2vOrk</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
         <v>5</v>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="n">
+        <v>0.04722447691197695</v>
+      </c>
       <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>-0.4713968731432203</v>
+      </c>
       <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
+      <c r="AB9" t="n">
+        <v>4.22146141236216</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>6105587.759105681</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4.580523000284018</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.5998769714762346</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="n">
-        <v>-0.6828342922318633</v>
-      </c>
+      <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="n">
-        <v>3.641528715641854</v>
-      </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="n">
-        <v>2.89386719422842</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>5269724.278337177</v>
-      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="n">
-        <v>3.732628239028202</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="n">
-        <v>0.05023674242424248</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1841,127 +1784,122 @@
   las palmas </t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>IyRQC2vM</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>h8oAv4Ts</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>148</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>1481</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>20242025</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>WC1tKXIF</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>bs5KnIiT</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-4</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>-2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-1</v>
       </c>
       <c r="R10" t="n">
         <v>-1</v>
       </c>
       <c r="S10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-5.331398809523847</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-3.417063492063498</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-2.89771825396825</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-3528839.285714285</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.499713564262124</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1.542509920634942</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-4.420193306155426</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-1.008035714285714</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-4.83139505767636</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-6063772.852581156</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-2.549894942201277</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.029229816189705</v>
+      </c>
+      <c r="AF10" t="n">
         <v>0</v>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="n">
-        <v>2.442062621597341</v>
-      </c>
+      <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="n">
-        <v>-6223015.873015871</v>
-      </c>
+      <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="n">
-        <v>-1.724206349206355</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-6.194618313230379</v>
-      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="n">
-        <v>-5.21487800028919</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>-7539604.471573318</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>-6.170634920634882</v>
-      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="n">
-        <v>-0.9880952380952372</v>
-      </c>
+      <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="n">
-        <v>-2.20634920634923</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-2.749197413124989</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-0.5992063492063489</v>
-      </c>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="n">
-        <v>-0.4634569208498232</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
+      <c r="AZ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1984,127 +1922,122 @@
   vigo </t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>8pvUZFhf</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>hxt57t2q</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>148</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>1481</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>20242025</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>UDgEKBbq</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>nDP2jHyH</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>2</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
+        <v>0.1567460317459961</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.351851851851851</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.785052910052912</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4040674.603174603</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1910443722943722</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.9660052910052883</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.8949773354665069</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.3888888888888888</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9335913482652671</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2979518.986448334</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.046884214819016</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.763488142292491</v>
+      </c>
+      <c r="AF11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="n">
-        <v>2.200462339779541</v>
-      </c>
+      <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="n">
-        <v>4132083.333333333</v>
-      </c>
+      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="n">
-        <v>1.668055555555554</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.133462152023284</v>
-      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="n">
-        <v>-1.476770130248894</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3450645.318005157</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.053240740740762</v>
-      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="n">
-        <v>3.193055555555553</v>
-      </c>
+      <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="n">
-        <v>3.582870370370372</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>3.739340505462295</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0.4513888888888886</v>
-      </c>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="n">
-        <v>0.2389297385620914</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
+      <c r="AZ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2127,127 +2060,122 @@
   sevilla </t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>vJbTeCGP</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>nNNpcUSL</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>148</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>1481</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>20242025</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>A7v4ruhp</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>8</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>3</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
+        <v>-0.3255952380952181</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.818650793650789</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-2.153174603174591</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-13656706.34920635</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.9011201577312842</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-3.971031746031727</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.754544479405041</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.521031746031746</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-1.853105022520083</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-4934973.836311791</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9128792883476819</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4.153374207711305</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0</v>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="n">
-        <v>3.648595116184126</v>
-      </c>
+      <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="n">
-        <v>-15000138.88888889</v>
-      </c>
+      <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="n">
-        <v>-3.954166666666666</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-1.360045357549239</v>
-      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="n">
-        <v>4.893591539179766</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-4429940.02256773</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.9902777777777771</v>
-      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
       <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="n">
-        <v>2.358333333333334</v>
-      </c>
+      <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="n">
-        <v>-3.333333333333343</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.247021966681402</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0.3972222222222221</v>
-      </c>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="n">
-        <v>0.8867192018507803</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
+      <c r="AZ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2270,127 +2198,122 @@
   bilbao </t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>IP5zl0cJ</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>dboeiWOt</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>148</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>1481</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>20242025</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>spain</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>laliga</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>0Q3vjDhH</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>p2dFnNso</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>4</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>-0.6975308641974891</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.9961033950617271</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.742631172839495</v>
+      </c>
+      <c r="W13" t="n">
+        <v>11175043.40277778</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.2329739092606744</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.854513888888889</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-2.964161662139588</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.1936342592592595</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.505077517117954</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7836670.359273762</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.616392965014299</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.6824135083326262</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="n">
-        <v>2.193480669770231</v>
-      </c>
+      <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="n">
-        <v>10639871.93362194</v>
-      </c>
+      <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="n">
-        <v>3.127651515151513</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>3.350490766217064</v>
-      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="n">
-        <v>-2.513752666186377</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7678496.106188629</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>-0.9702380952380452</v>
-      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="n">
-        <v>-0.2917748917748924</v>
-      </c>
+      <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="n">
-        <v>3.039880952380955</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5.080437941926078</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0.2916486291486293</v>
-      </c>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="n">
-        <v>0.3660127951723109</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
+      <c r="AZ13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
